--- a/0176_Cuenca_Coata/_raw_reportes_xlsx/IDConfig_64955_completo.xlsx
+++ b/0176_Cuenca_Coata/_raw_reportes_xlsx/IDConfig_64955_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R83f6115d95324202"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R4394916e5c8c47fa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.9187</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.9754</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.9754</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.4483</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.3968</x:v>
+        <x:v>      6.8711</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -279,7 +414,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.0173</x:v>
+        <x:v>      7.4561</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +429,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +444,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +459,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +474,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.0304</x:v>
+        <x:v>      8.3595</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -354,7 +489,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -369,7 +504,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.9508</x:v>
+        <x:v>      8.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -384,7 +519,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -399,7 +534,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.6210</x:v>
+        <x:v>      8.0024</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -414,7 +549,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -429,7 +564,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -444,7 +579,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -459,7 +594,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -474,7 +609,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -489,7 +624,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.9627</x:v>
+        <x:v>      8.2948</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -504,7 +639,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -519,7 +654,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -534,7 +669,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -549,7 +684,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -564,7 +699,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -579,7 +714,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -594,7 +729,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -609,7 +744,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.7382</x:v>
+        <x:v>      8.9556</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -624,7 +759,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -639,7 +774,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.4139</x:v>
+        <x:v>      9.5026</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -654,7 +789,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -669,7 +804,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -684,7 +819,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -699,7 +834,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -714,7 +849,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -729,7 +864,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -744,7 +879,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -759,7 +894,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -774,7 +909,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -789,7 +924,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.2132</x:v>
+        <x:v>      9.3429</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -804,7 +939,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.2132</x:v>
+        <x:v>      9.3429</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -819,7 +954,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3136</x:v>
+        <x:v>      9.4227</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -834,7 +969,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.0215</x:v>
+        <x:v>      9.1872</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -849,7 +984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -864,7 +999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -879,7 +1014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -894,7 +1029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -909,7 +1044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -924,7 +1059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -939,7 +1074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.2132</x:v>
+        <x:v>      9.3429</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -954,7 +1089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -969,7 +1104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -984,7 +1119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -999,7 +1134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1014,7 +1149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1029,7 +1164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1044,7 +1179,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1059,7 +1194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1074,7 +1209,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1089,7 +1224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1104,7 +1239,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1119,7 +1254,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.9295</x:v>
+        <x:v>      9.9076</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1134,7 +1269,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.4184</x:v>
+        <x:v>      9.5045</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1149,7 +1284,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1164,7 +1299,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1179,7 +1314,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1194,7 +1329,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1209,7 +1344,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1224,7 +1359,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.0345</x:v>
+        <x:v>      9.9894</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1239,7 +1374,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.1893</x:v>
+        <x:v>     10.0919</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1254,7 +1389,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5883</x:v>
+        <x:v>     10.4107</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1269,7 +1404,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1284,7 +1419,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.0345</x:v>
+        <x:v>      9.9894</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1299,7 +1434,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1314,7 +1449,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.1443</x:v>
+        <x:v>     10.0733</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1329,7 +1464,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1344,7 +1479,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.9739</x:v>
+        <x:v>     10.6851</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1359,7 +1494,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.3056</x:v>
+        <x:v>     11.6576</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1374,7 +1509,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.8460</x:v>
+        <x:v>     12.0333</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1389,7 +1524,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5523</x:v>
+        <x:v>     12.5145</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1404,7 +1539,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.7009</x:v>
+        <x:v>     12.6135</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1419,7 +1554,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.2509</x:v>
+        <x:v>     13.6259</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1434,7 +1569,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     15.1591</x:v>
+        <x:v>     14.8101</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1449,7 +1584,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     16.4826</x:v>
+        <x:v>     15.6001</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1464,7 +1599,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.9453</x:v>
+        <x:v>     14.0567</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1479,7 +1614,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.4122</x:v>
+        <x:v>     11.0204</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1494,7 +1629,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1509,7 +1644,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.2540</x:v>
+        <x:v>     10.1571</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1524,7 +1659,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.3638</x:v>
+        <x:v>     10.2410</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1539,7 +1674,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.7398</x:v>
+        <x:v>      7.8761</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1554,7 +1689,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1569,7 +1704,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.7031</x:v>
+        <x:v>     10.4966</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1584,7 +1719,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.2923</x:v>
+        <x:v>     10.9324</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1599,7 +1734,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.4122</x:v>
+        <x:v>     11.0204</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1614,7 +1749,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.4122</x:v>
+        <x:v>     11.0204</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1629,7 +1764,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.8636</x:v>
+        <x:v>     12.0399</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1644,7 +1779,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1466</x:v>
+        <x:v>     12.9103</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1659,7 +1794,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.7664</x:v>
+        <x:v>     13.3152</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1674,7 +1809,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.7557</x:v>
+        <x:v>     13.9436</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1689,7 +1824,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     15.5169</x:v>
+        <x:v>     15.0291</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1704,7 +1839,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     16.2771</x:v>
+        <x:v>     15.4819</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1719,7 +1854,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     20.3311</x:v>
+        <x:v>     17.7723</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1734,7 +1869,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     23.0869</x:v>
+        <x:v>     19.1573</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1749,7 +1884,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     23.5597</x:v>
+        <x:v>     19.4753</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1764,7 +1899,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     24.5047</x:v>
+        <x:v>     21.1430</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1779,7 +1914,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.6945</x:v>
+        <x:v>     23.7154</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1794,7 +1929,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.1464</x:v>
+        <x:v>     24.8240</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1809,7 +1944,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     25.5620</x:v>
+        <x:v>     24.1817</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1824,7 +1959,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.4427</x:v>
+        <x:v>     25.1514</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1839,7 +1974,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     27.9486</x:v>
+        <x:v>     26.8263</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1854,7 +1989,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     28.5655</x:v>
+        <x:v>     27.5195</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1869,7 +2004,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     30.6335</x:v>
+        <x:v>     30.0514</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1884,7 +2019,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.1385</x:v>
+        <x:v>     34.8343</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1899,7 +2034,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.3388</x:v>
+        <x:v>     33.7436</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1914,7 +2049,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.1817</x:v>
+        <x:v>     36.2448</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1929,7 +2064,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     39.7381</x:v>
+        <x:v>     42.2352</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1944,7 +2079,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.8520</x:v>
+        <x:v>     51.1602</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1959,7 +2094,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     43.0139</x:v>
+        <x:v>     46.4046</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1974,7 +2109,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5349</x:v>
+        <x:v>     36.7179</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1989,7 +2124,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.5369</x:v>
+        <x:v>     36.7190</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2004,7 +2139,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.2820</x:v>
+        <x:v>     33.6659</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2019,7 +2154,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.1817</x:v>
+        <x:v>     36.2448</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2034,7 +2169,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.1666</x:v>
+        <x:v>     38.8698</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2049,7 +2184,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     42.4152</x:v>
+        <x:v>     45.6577</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2064,7 +2199,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0138</x:v>
+        <x:v>     50.1426</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2079,7 +2214,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     48.5752</x:v>
+        <x:v>     53.2204</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2094,7 +2229,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     59.9336</x:v>
+        <x:v>     66.5562</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2109,7 +2244,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     63.6665</x:v>
+        <x:v>     70.6904</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2124,7 +2259,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     62.7794</x:v>
+        <x:v>     69.7876</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2139,7 +2274,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     68.0738</x:v>
+        <x:v>     75.6595</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2154,7 +2289,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     84.3261</x:v>
+        <x:v>     92.9105</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2169,7 +2304,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     79.6188</x:v>
+        <x:v>     88.0614</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2184,7 +2319,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.4450</x:v>
+        <x:v>     88.9313</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2199,7 +2334,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     79.9680</x:v>
+        <x:v>     88.3913</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2214,7 +2349,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     86.9183</x:v>
+        <x:v>     95.5346</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2229,7 +2364,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     78.5308</x:v>
+        <x:v>     86.9089</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2244,7 +2379,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     91.0471</x:v>
+        <x:v>     99.8828</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2259,7 +2394,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    113.7600</x:v>
+        <x:v>    122.3192</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2274,7 +2409,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    144.4330</x:v>
+        <x:v>    151.0336</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2289,7 +2424,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    130.9497</x:v>
+        <x:v>    138.6658</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2304,7 +2439,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    150.7342</x:v>
+        <x:v>    156.6973</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2319,7 +2454,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    146.9055</x:v>
+        <x:v>    153.3578</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2334,7 +2469,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    161.3958</x:v>
+        <x:v>    166.4110</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2349,7 +2484,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    158.8340</x:v>
+        <x:v>    164.0386</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2364,7 +2499,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    110.0738</x:v>
+        <x:v>    118.2102</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2379,7 +2514,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     98.7465</x:v>
+        <x:v>    107.5722</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2394,7 +2529,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    115.3555</x:v>
+        <x:v>    123.8871</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2409,7 +2544,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     96.5645</x:v>
+        <x:v>    105.1228</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2424,7 +2559,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     61.5232</x:v>
+        <x:v>     67.8387</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2439,7 +2574,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.2208</x:v>
+        <x:v>     50.3956</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2454,7 +2589,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.7829</x:v>
+        <x:v>     54.7198</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2469,7 +2604,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     51.1246</x:v>
+        <x:v>     56.2916</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2484,7 +2619,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     52.8173</x:v>
+        <x:v>     58.3354</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2499,7 +2634,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     61.1069</x:v>
+        <x:v>     67.8958</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2514,7 +2649,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     72.9048</x:v>
+        <x:v>     80.9047</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2529,7 +2664,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     83.1671</x:v>
+        <x:v>     91.6726</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2544,7 +2679,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    106.8012</x:v>
+        <x:v>    115.5946</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2559,7 +2694,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    140.1782</x:v>
+        <x:v>    147.0405</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2574,7 +2709,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    140.3325</x:v>
+        <x:v>    147.1239</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2589,7 +2724,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    112.4791</x:v>
+        <x:v>    120.9213</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2604,7 +2739,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     59.0552</x:v>
+        <x:v>     64.6703</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2619,7 +2754,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     39.6251</x:v>
+        <x:v>     42.0331</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2634,7 +2769,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.6250</x:v>
+        <x:v>     34.1335</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2649,7 +2784,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     37.7573</x:v>
+        <x:v>     39.5951</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2664,7 +2799,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     24.8406</x:v>
+        <x:v>     21.4947</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2679,7 +2814,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     18.7898</x:v>
+        <x:v>     16.9137</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2694,7 +2829,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     21.0524</x:v>
+        <x:v>     18.1584</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2709,7 +2844,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.6458</x:v>
+        <x:v>     21.0157</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2724,7 +2859,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     29.5640</x:v>
+        <x:v>     28.8115</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2739,7 +2874,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     25.7568</x:v>
+        <x:v>     24.3958</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2754,7 +2889,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     27.3418</x:v>
+        <x:v>     26.1493</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2769,7 +2904,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     28.2591</x:v>
+        <x:v>     27.1762</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2784,7 +2919,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.1049</x:v>
+        <x:v>     32.0419</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2799,7 +2934,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     36.4238</x:v>
+        <x:v>     37.9039</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2814,7 +2949,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     40.4870</x:v>
+        <x:v>     43.2044</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2829,7 +2964,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     42.4294</x:v>
+        <x:v>     45.6654</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2844,7 +2979,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.2623</x:v>
+        <x:v>     47.7849</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2859,7 +2994,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     39.9269</x:v>
+        <x:v>     42.4784</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2874,7 +3009,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     42.8069</x:v>
+        <x:v>     46.1516</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2889,7 +3024,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.2269</x:v>
+        <x:v>     50.3990</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2904,7 +3039,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     56.1908</x:v>
+        <x:v>     62.2754</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2919,7 +3054,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     66.5345</x:v>
+        <x:v>     73.9339</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2934,7 +3069,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     89.2932</x:v>
+        <x:v>     98.0882</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2949,7 +3084,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     82.0389</x:v>
+        <x:v>     89.6518</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2964,7 +3099,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.4650</x:v>
+        <x:v>     51.9148</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2979,7 +3114,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.6660</x:v>
+        <x:v>     52.1645</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2994,7 +3129,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.0138</x:v>
+        <x:v>     50.1426</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3009,7 +3144,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     53.0487</x:v>
+        <x:v>     58.6016</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3024,7 +3159,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     61.8782</x:v>
+        <x:v>     68.7361</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3039,7 +3174,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     65.5115</x:v>
+        <x:v>     72.8165</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3054,7 +3189,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     85.9338</x:v>
+        <x:v>     94.5791</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3069,7 +3204,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    116.8739</x:v>
+        <x:v>    125.2723</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3084,7 +3219,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     95.8559</x:v>
+        <x:v>    104.7398</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3099,7 +3234,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    120.8039</x:v>
+        <x:v>    129.0898</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3114,7 +3249,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    144.5711</x:v>
+        <x:v>    151.1083</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3129,7 +3264,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    125.6373</x:v>
+        <x:v>    133.6778</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3144,7 +3279,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    171.3166</x:v>
+        <x:v>    175.3011</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3159,7 +3294,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    192.3844</x:v>
+        <x:v>    193.6029</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3174,7 +3309,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    216.6215</x:v>
+        <x:v>    214.1822</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3189,7 +3324,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    126.6990</x:v>
+        <x:v>    134.6749</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3204,7 +3339,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    175.4132</x:v>
+        <x:v>    178.7854</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3219,7 +3354,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    120.7633</x:v>
+        <x:v>    129.0678</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3234,7 +3369,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    127.0298</x:v>
+        <x:v>    134.9949</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3249,7 +3384,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    128.5056</x:v>
+        <x:v>    136.3570</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3264,7 +3399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    148.7691</x:v>
+        <x:v>    155.0706</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3279,7 +3414,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    193.2371</x:v>
+        <x:v>    194.3460</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3294,7 +3429,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    108.1273</x:v>
+        <x:v>    116.0292</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3309,7 +3444,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    112.7348</x:v>
+        <x:v>    121.3417</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3324,7 +3459,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    187.7985</x:v>
+        <x:v>    189.7131</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3339,7 +3474,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    178.8868</x:v>
+        <x:v>    181.5096</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3354,7 +3489,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    105.0129</x:v>
+        <x:v>    113.7814</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3369,7 +3504,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    120.0751</x:v>
+        <x:v>    128.4136</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3384,7 +3519,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    126.3660</x:v>
+        <x:v>    134.3539</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3399,7 +3534,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     67.9960</x:v>
+        <x:v>     75.5705</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3414,7 +3549,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     63.9873</x:v>
+        <x:v>     70.8638</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3429,7 +3564,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     41.7049</x:v>
+        <x:v>     44.5683</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3444,7 +3579,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     21.0524</x:v>
+        <x:v>     18.1584</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3459,7 +3594,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     17.8912</x:v>
+        <x:v>     16.4175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3474,7 +3609,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     14.7940</x:v>
+        <x:v>     14.5886</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3489,7 +3624,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     17.2976</x:v>
+        <x:v>     16.0704</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3504,7 +3639,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     22.0328</x:v>
+        <x:v>     18.6787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3519,7 +3654,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.9144</x:v>
+        <x:v>     21.1526</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3534,7 +3669,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     27.9526</x:v>
+        <x:v>     26.8328</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3549,7 +3684,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.1258</x:v>
+        <x:v>     33.4403</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3564,7 +3699,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     41.8306</x:v>
+        <x:v>     44.9184</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3579,7 +3714,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     30.0876</x:v>
+        <x:v>     29.6416</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3594,7 +3729,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     30.6602</x:v>
+        <x:v>     22.9341</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3609,7 +3744,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     29.3775</x:v>
+        <x:v>     22.3314</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3624,7 +3759,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     29.5318</x:v>
+        <x:v>     23.4066</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/0176_Cuenca_Coata/_raw_reportes_xlsx/IDConfig_64955_completo.xlsx
+++ b/0176_Cuenca_Coata/_raw_reportes_xlsx/IDConfig_64955_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R4394916e5c8c47fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rdbad1b5604914f5c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.9754</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0887</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.9187</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0920</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.4417</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.9344</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.9344</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0643</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0061</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.1909</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.5913</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1430</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4354</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.5877</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.5210</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8725</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.9344</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.6847</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.6231</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.9344</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.5877</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3208</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.1909</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8129</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8112</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.6280</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.4483</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.2053</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5016</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5016</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.4434</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.4433</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.4417</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
